--- a/correctionProfile/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:57:50+00:00</t>
+    <t>2026-09-17T15:33:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correctionProfile/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T15:33:46+00:00</t>
+    <t>2026-09-28T13:37:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -22642,10 +22642,10 @@
       </c>
       <c r="E166" s="2"/>
       <c r="F166" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G166" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H166" t="s" s="2">
         <v>81</v>
@@ -24050,10 +24050,10 @@
       </c>
       <c r="E178" s="2"/>
       <c r="F178" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G178" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H178" t="s" s="2">
         <v>81</v>

--- a/correctionProfile/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T13:37:45+00:00</t>
+    <t>2026-09-29T08:08:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2372,7 +2372,7 @@
     <t>The nature of the relationship. Rôle de la personne. Ex : personne de confiance, aidant ...</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-role-informateur-cisis|20260716085852</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-role-informateur-cisis|20260916095455</t>
   </si>
   <si>
     <t>Patient.contact.relationship:Role.id</t>

--- a/correctionProfile/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T08:08:01+00:00</t>
+    <t>2026-09-29T09:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -22642,10 +22642,10 @@
       </c>
       <c r="E166" s="2"/>
       <c r="F166" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G166" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H166" t="s" s="2">
         <v>81</v>
@@ -24050,10 +24050,10 @@
       </c>
       <c r="E178" s="2"/>
       <c r="F178" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G178" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H178" t="s" s="2">
         <v>81</v>
